--- a/ab_plugin_IF_analysis/utils/method_input.xlsx
+++ b/ab_plugin_IF_analysis/utils/method_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mael.mouhoub\Documents\Recherche\Git_coding\Criticality\Plugin Titouan\plugin_test\utils\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mael.mouhoub\Documents\2-Recherche\5-Git_repositories\ab-plugin-IF_analysis\ab_plugin_IF_analysis\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760F40D4-66CA-4133-A170-1487C0439354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576AF032-ACCE-48C1-A1A5-6D332BF84FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="4980" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9228" yWindow="2334" windowWidth="15330" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="285">
   <si>
     <t>GLO</t>
   </si>
@@ -82,6 +82,804 @@
   </si>
   <si>
     <t>Method 3</t>
+  </si>
+  <si>
+    <t>crm</t>
+  </si>
+  <si>
+    <t>aluminium oxide, metallurgical</t>
+  </si>
+  <si>
+    <t>market for aluminium oxide, metallurgical</t>
+  </si>
+  <si>
+    <t>IAI Area, Asia, without China and GCC</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '8aacfd62fca4bfa1ad986b651deb8f9d')</t>
+  </si>
+  <si>
+    <t>aluminium</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '642a9155ba85f790521ce2d48f6e3821')</t>
+  </si>
+  <si>
+    <t>RoW</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'd4540c46f683bd26a83c5494e9ffb50b')</t>
+  </si>
+  <si>
+    <t>IAI Area, Western and Central Europe</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'd6aaedba43d5049debbbd2117d1ab8e1')</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '60e94100a96f16fb5c64eb7a0c0970fe')</t>
+  </si>
+  <si>
+    <t>IAI Area, South America</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'e41e7884d02ebc24e44663890aaa82aa')</t>
+  </si>
+  <si>
+    <t>IAI Area, Gulf Cooperation Council</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'a178247d801691aacb70f8b2fc1fc9e2')</t>
+  </si>
+  <si>
+    <t>UN-OCEANIA</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '01f81e862c52606f8132dcaf63a3b5c7')</t>
+  </si>
+  <si>
+    <t>aluminium oxide, non-metallurgical</t>
+  </si>
+  <si>
+    <t>market for aluminium oxide, non-metallurgical</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '8b6c42066aa6f84aa9c29426f2f40197')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '7b2d97a5bfc16b2540adc6e81b340b1e')</t>
+  </si>
+  <si>
+    <t>aluminium hydroxide</t>
+  </si>
+  <si>
+    <t>market for aluminium hydroxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'fc4f8123e413f1bb91efe8f3e78b134f')</t>
+  </si>
+  <si>
+    <t>treatment of aluminium scrap, new, at refiner</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '6bef1a839f92e451239f2cc40d68c7f9')</t>
+  </si>
+  <si>
+    <t>RER</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '3dc408a2e82e05c2fba5f1cc1e07f5cc')</t>
+  </si>
+  <si>
+    <t>aluminium, cast alloy</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '95f483050b538cedf69d706ab94655ea')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'dc1d90af7122519e48a8c4c0ebf95710')</t>
+  </si>
+  <si>
+    <t>treatment of aluminium scrap, post-consumer, prepared for recycling, at refiner</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'c2c83e75baa4e2351e7b7d667799440b')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '1723ccac16315b4753b0e85691d806b9')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'b8dbf47a74537e1f1b40ae00439533b0')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '6535747aac81d8419a415c37d1e530b4')</t>
+  </si>
+  <si>
+    <t>aluminium, wrought alloy</t>
+  </si>
+  <si>
+    <t>treatment of aluminium scrap, new, at remelter</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'cdd7a56f10f6b885c064b0f195c1111c')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '3870265447ca438e84804e1645e4993d')</t>
+  </si>
+  <si>
+    <t>cerium oxide</t>
+  </si>
+  <si>
+    <t>market for cerium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '6fd09262c0ef200ddd1a6e26f70427b0')</t>
+  </si>
+  <si>
+    <t>cerium</t>
+  </si>
+  <si>
+    <t>lanthanum-cerium oxide</t>
+  </si>
+  <si>
+    <t>market for lanthanum-cerium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '2f511e17eb56009103c9d167d8add618')</t>
+  </si>
+  <si>
+    <t>cobalt</t>
+  </si>
+  <si>
+    <t>market for cobalt</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '6e767e454e0e1723b9759536a30d333c')</t>
+  </si>
+  <si>
+    <t>cobalt acetate</t>
+  </si>
+  <si>
+    <t>market for cobalt acetate</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '3fc86439e59c8b7396970f8b8d92c946')</t>
+  </si>
+  <si>
+    <t>cobalt carbonate</t>
+  </si>
+  <si>
+    <t>market for cobalt carbonate</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '909b658eac73d8cefb2cf0700837c771')</t>
+  </si>
+  <si>
+    <t>cobalt hydroxide</t>
+  </si>
+  <si>
+    <t>market for cobalt hydroxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'abc08c782e4611f2a8c2b09b0b49d5c2')</t>
+  </si>
+  <si>
+    <t>cobalt oxide</t>
+  </si>
+  <si>
+    <t>market for cobalt oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'b2918b9964d48355cd24b24b6bb000b5')</t>
+  </si>
+  <si>
+    <t>copper sulfate</t>
+  </si>
+  <si>
+    <t>primary zinc production from concentrate</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '8445b459b04c1e0fb21f0947a1fb9e02')</t>
+  </si>
+  <si>
+    <t>copper</t>
+  </si>
+  <si>
+    <t>copper, anode</t>
+  </si>
+  <si>
+    <t>market for copper, anode</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '0fa3f1aa4033ea554eedfee204aaf3e1')</t>
+  </si>
+  <si>
+    <t>copper, cathode</t>
+  </si>
+  <si>
+    <t>aluminium alloy production, AlLi</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '7224d6a5b18209a8efeafb74515a1969')</t>
+  </si>
+  <si>
+    <t>CA-QC</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'f331fb737185c99cd182f4b37a171132')</t>
+  </si>
+  <si>
+    <t>aluminium alloy production, Metallic Matrix Composite</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '24b23891ee8433001105c34200761163')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'bc243bbb4849af987f49044594548ee3')</t>
+  </si>
+  <si>
+    <t>cobalt production</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '4dbd2871d87d987338ac6943b6c4214c')</t>
+  </si>
+  <si>
+    <t>copper production, cathode, solvent extraction and electrowinning process</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '23892fc381914bdb315d61ec5cac7f73')</t>
+  </si>
+  <si>
+    <t>gold mine operation and refining</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '560b998c493428d4930b479f4a488d38')</t>
+  </si>
+  <si>
+    <t>platinum group metal mine operation, ore with high palladium content</t>
+  </si>
+  <si>
+    <t>RU</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '7383ffa092989743b144e22c0f11efab')</t>
+  </si>
+  <si>
+    <t>platinum group metal, extraction and refinery operations</t>
+  </si>
+  <si>
+    <t>ZA</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '892ed9b65ade3c7f055d5a51642c7ad2')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '1b8c7ee70b64193d1c6fc0d8ec7aee67')</t>
+  </si>
+  <si>
+    <t>treatment of copper cake</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'eed3bf5fa90e3e3b493c8f3d75a5cf58')</t>
+  </si>
+  <si>
+    <t>treatment of metal part of electronics scrap, in copper, anode, by electrolytic refining</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'bb56a4316b0c0f4ded2fc5d0a1d15a36')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'd4e02ad9200c5a3759366ea63fe984ea')</t>
+  </si>
+  <si>
+    <t>treatment of non-Fe-Co-metals, from used Li-ion battery, hydrometallurgical processing</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '74c6e097ebb2c76d145be87108187edb')</t>
+  </si>
+  <si>
+    <t>treatment of non-Fe-Co-metals, from used Li-ion battery, pyrometallurgical processing</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '9c7765970ccfb1f4fd4d3fe839376ec9')</t>
+  </si>
+  <si>
+    <t>treatment of used cable</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '234f1d9f5feda3b87d9cf699f5153a6a')</t>
+  </si>
+  <si>
+    <t>electrolyte, copper-rich</t>
+  </si>
+  <si>
+    <t>market for electrolyte, copper-rich</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'f5750143a97915fe2f292a47389490e9')</t>
+  </si>
+  <si>
+    <t>stockpiling of anode slime from electrorefining of copper, anode</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '71926fa56b2d68cbdf76c6b048c5ee8d')</t>
+  </si>
+  <si>
+    <t>treatment of copper scrap by electrolytic refining</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'a8de1828eb5593271e36728d356fffde')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '09e5754f308357d0535d9c20da201d34')</t>
+  </si>
+  <si>
+    <t>terbium-dysprosium oxide</t>
+  </si>
+  <si>
+    <t>market for terbium-dysprosium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'f0f540ef65bb1008cf49abc000b76ca4')</t>
+  </si>
+  <si>
+    <t>dysprosium</t>
+  </si>
+  <si>
+    <t>dysprosium oxide</t>
+  </si>
+  <si>
+    <t>market for dysprosium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'a4442902d58129df1f5099033245a51e')</t>
+  </si>
+  <si>
+    <t>samarium-europium-gadolinium oxide</t>
+  </si>
+  <si>
+    <t>market for samarium-europium-gadolinium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '02b7c820f5f6af3786ddad70f6647602')</t>
+  </si>
+  <si>
+    <t>europium</t>
+  </si>
+  <si>
+    <t>europium oxide</t>
+  </si>
+  <si>
+    <t>market for europium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '7d23bfc274062b1c50e1331c12d8d5bb')</t>
+  </si>
+  <si>
+    <t>gadolinium</t>
+  </si>
+  <si>
+    <t>gadolinium oxide</t>
+  </si>
+  <si>
+    <t>market for gadolinium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '5c576fe28fc4efef32338e2869be90f7')</t>
+  </si>
+  <si>
+    <t>aluminium alloy, AlLi</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '56ce544b95136adf129a33151682d535')</t>
+  </si>
+  <si>
+    <t>lithium</t>
+  </si>
+  <si>
+    <t>lithium aluminium hydride</t>
+  </si>
+  <si>
+    <t>lithium aluminium hydride production, from lithium hydride and aluminium chloride</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '6f585dbf9bf89037e0f64b5e5d28c612')</t>
+  </si>
+  <si>
+    <t>lithium chloride</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '31a2c6d51318930973129102bede30bc')</t>
+  </si>
+  <si>
+    <t>lithium fluoride</t>
+  </si>
+  <si>
+    <t>lithium fluoride production</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '97380e6f935e8eb3113a78507cfe25b6')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '370eafbafc47df0ef52cae8c709b0a0a')</t>
+  </si>
+  <si>
+    <t>lithium hexafluorophosphate</t>
+  </si>
+  <si>
+    <t>lithium hexafluorophosphate production</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'acace4f73ea8216e8cf1881f91ac5f5a')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '2e6d8f702a1ab438e64a3d0acbc81a42')</t>
+  </si>
+  <si>
+    <t>lithium sulfate</t>
+  </si>
+  <si>
+    <t>lithium iron phosphate production, hydrothermal process</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'bbcaef5819ea4fdec65f8d1d91f08d32')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'a90c3a8ff66f89db888be52f748e20f0')</t>
+  </si>
+  <si>
+    <t>lithium iron phosphate</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '6a829fec48111ec45c2c6f996ed77965')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '269f3d2901f9044aa069137a1643e4cc')</t>
+  </si>
+  <si>
+    <t>lithium iron phosphate production, solid state process</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '05b1ec269c5558c4862e9d3d6db0ed92')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '309fcd903260757e0e145063c713dd01')</t>
+  </si>
+  <si>
+    <t>lithium manganese oxide</t>
+  </si>
+  <si>
+    <t>lithium manganese oxide production</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '73a5402708d0489b1d76fc47ced8729e')</t>
+  </si>
+  <si>
+    <t>lithium sulfate production</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '48a25ab8b4b38aa12ee3441a26eec165')</t>
+  </si>
+  <si>
+    <t>lithium titanate spinel</t>
+  </si>
+  <si>
+    <t>lithium titanate spinel production</t>
+  </si>
+  <si>
+    <t>UN-EASIA</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'aa5ece6177366edfe4cbacf3504d835f')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '2a0e6ab2d021080eca70af2b1f4f9860')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'ca85b2508992755882b9ffb24bbb1a69')</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'cfe643ab7f206734e021049be3041f0c')</t>
+  </si>
+  <si>
+    <t>manganese carbonate production</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '9aba6fe81f5a496e604d407e58282001')</t>
+  </si>
+  <si>
+    <t>NCA oxide</t>
+  </si>
+  <si>
+    <t>NCA oxide production, for Li-ion battery</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '0c3b50a8f0047be32a162dc70dd00ac9')</t>
+  </si>
+  <si>
+    <t>NMC111 oxide</t>
+  </si>
+  <si>
+    <t>NMC111 oxide production, for Li-ion battery</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '62e3ab4de522d8823fdf78e49ef6bc7d')</t>
+  </si>
+  <si>
+    <t>phthalimide-compound</t>
+  </si>
+  <si>
+    <t>phthalimide-compound production</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '37b716c466802e9b4bbfd0678fcbfbc1')</t>
+  </si>
+  <si>
+    <t>lanthanum oxide</t>
+  </si>
+  <si>
+    <t>market for lanthanum oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '94256e182c18fd6fc6a6a8773994b486')</t>
+  </si>
+  <si>
+    <t>lanthanum</t>
+  </si>
+  <si>
+    <t>neodymium oxide</t>
+  </si>
+  <si>
+    <t>market for neodymium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '6ae8d45d5a8c04bd02eed9a0c5ada868')</t>
+  </si>
+  <si>
+    <t>neodymium</t>
+  </si>
+  <si>
+    <t>praseodymium-neodymium oxide</t>
+  </si>
+  <si>
+    <t>market for praseodymium-neodymium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'd1875d8292346c6897620d2e1b54830e')</t>
+  </si>
+  <si>
+    <t>ferronickel</t>
+  </si>
+  <si>
+    <t>market for ferronickel</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '770ec234c4d443487de69f7f4ee3ff18')</t>
+  </si>
+  <si>
+    <t>nickel</t>
+  </si>
+  <si>
+    <t>nickel concentrate, 7% Ni</t>
+  </si>
+  <si>
+    <t>market for nickel concentrate, 7% Ni</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '566e646c3060e24532cf9583e2d0a630')</t>
+  </si>
+  <si>
+    <t>nickel sulfate</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'e1a23c732e4adef3a7794019d9229999')</t>
+  </si>
+  <si>
+    <t>nickel, class 1</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'd73d7693cf436c80294fec53649834f6')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '743bc82c79e3f7f142326a24dfc9988c')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'c2cb9138fd5bdd6b1eca40028969b8c5')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '4d86442405e5cbbc4fb4795d34e90eb5')</t>
+  </si>
+  <si>
+    <t>smelting and refining of nickel concentrate, 16% Ni</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '10ba1c6696a20088f390460b38eb2438')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'b91f22c68732481f9eaffbb8bac609ed')</t>
+  </si>
+  <si>
+    <t>market for nickel, class 1</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'f1abd7afb255dd85914728cbf4e7f9f2')</t>
+  </si>
+  <si>
+    <t>smelting and refining of nickel concentrate, 7% Ni</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '59f06bfb8addba6e2d024568fbf4d108')</t>
+  </si>
+  <si>
+    <t>nickel-rich materials</t>
+  </si>
+  <si>
+    <t>market for nickel-rich materials</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'de69b573a55e7d16284ddc11d578389f')</t>
+  </si>
+  <si>
+    <t>palladium</t>
+  </si>
+  <si>
+    <t>market for palladium</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '9e444c6755c1f4312373b05cedd7eafa')</t>
+  </si>
+  <si>
+    <t>platinum</t>
+  </si>
+  <si>
+    <t>market for platinum</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '5862511455a866734523bfc25cd1ba07')</t>
+  </si>
+  <si>
+    <t>praseodymium</t>
+  </si>
+  <si>
+    <t>praseodymium oxide</t>
+  </si>
+  <si>
+    <t>market for praseodymium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'fe27a40610e5fb43532bfe42e2cfeece')</t>
+  </si>
+  <si>
+    <t>rhodium</t>
+  </si>
+  <si>
+    <t>market for rhodium</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '364a55cd4b4923b5714d1466c8f4252f')</t>
+  </si>
+  <si>
+    <t>silicon, metallurgical grade</t>
+  </si>
+  <si>
+    <t>market for silicon, metallurgical grade</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '5a932d84f754ec53a3d626620992e64f')</t>
+  </si>
+  <si>
+    <t>silicon</t>
+  </si>
+  <si>
+    <t>silicon carbide</t>
+  </si>
+  <si>
+    <t>market for silicon carbide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '710395e8b43ccda813f25b37bca7728c')</t>
+  </si>
+  <si>
+    <t>silicon tetrachloride</t>
+  </si>
+  <si>
+    <t>zirconium and hafnium tetrachloride production, from zircon</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '76a1a81b05ee8b0933a8bbf46bcecbce')</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'abacb2bcc2a874b96c0e35b421f2690f')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '527d77b9c8eee4597584a4a428378a50')</t>
+  </si>
+  <si>
+    <t>ferrosilicon</t>
+  </si>
+  <si>
+    <t>ferrosilicon production</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'dfad8c52d38f98d542c5a73f1140529f')</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '1fbbee64e660e40bf3d2e5b35fc31446')</t>
+  </si>
+  <si>
+    <t>zamak ingot, 10% primary zinc input</t>
+  </si>
+  <si>
+    <t>zamak ingot production, 10% primary zinc input</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '34545784b4e633b8df5b7dd8fab12d14')</t>
+  </si>
+  <si>
+    <t>strontium carbonate</t>
+  </si>
+  <si>
+    <t>market for strontium carbonate</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '00badc540c4a91131694e974d1f13e31')</t>
+  </si>
+  <si>
+    <t>strontium</t>
+  </si>
+  <si>
+    <t>terbium oxide</t>
+  </si>
+  <si>
+    <t>market for terbium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'a36b6372f1864c77a680d127e03a5cfe')</t>
+  </si>
+  <si>
+    <t>terbium</t>
+  </si>
+  <si>
+    <t>titanium sponge</t>
+  </si>
+  <si>
+    <t>market for titanium sponge</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', 'e684e30bc72b6ca915db7cd484584f33')</t>
+  </si>
+  <si>
+    <t>titanium</t>
+  </si>
+  <si>
+    <t>yttrium oxide</t>
+  </si>
+  <si>
+    <t>market for yttrium oxide</t>
+  </si>
+  <si>
+    <t>('ecoinvent-3.12-cutoff', '3654e688e05b6155f8a9bc82760345b8')</t>
+  </si>
+  <si>
+    <t>yttrium</t>
+  </si>
+  <si>
+    <t>SH2E</t>
   </si>
 </sst>
 </file>
@@ -399,14 +1197,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I120"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="6" max="6" width="20.90625" customWidth="1"/>
-    <col min="8" max="8" width="21.6328125" customWidth="1"/>
+    <col min="6" max="6" width="20.89453125" customWidth="1"/>
+    <col min="8" max="8" width="21.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -431,8 +1229,11 @@
       <c r="H1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -454,8 +1255,11 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -477,8 +1281,11 @@
       <c r="H3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -500,8 +1307,11 @@
       <c r="H4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -523,8 +1333,11 @@
       <c r="H5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -546,8 +1359,11 @@
       <c r="H6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -568,6 +1384,2947 @@
       </c>
       <c r="H7" t="s">
         <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>284</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>284</v>
+      </c>
+      <c r="I10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H11" t="s">
+        <v>284</v>
+      </c>
+      <c r="I11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>284</v>
+      </c>
+      <c r="I12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>284</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>284</v>
+      </c>
+      <c r="I14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H15" t="s">
+        <v>284</v>
+      </c>
+      <c r="I15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H16" t="s">
+        <v>284</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>284</v>
+      </c>
+      <c r="I17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18">
+        <v>4.4275200000000002E-8</v>
+      </c>
+      <c r="H18" t="s">
+        <v>284</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>284</v>
+      </c>
+      <c r="I19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H20" t="s">
+        <v>284</v>
+      </c>
+      <c r="I20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21">
+        <v>1.2800000000000001E-7</v>
+      </c>
+      <c r="H21" t="s">
+        <v>284</v>
+      </c>
+      <c r="I21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22">
+        <v>1.2800000000000001E-7</v>
+      </c>
+      <c r="H22" t="s">
+        <v>284</v>
+      </c>
+      <c r="I22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H23" t="s">
+        <v>284</v>
+      </c>
+      <c r="I23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24">
+        <v>6.7750400000000003E-8</v>
+      </c>
+      <c r="H24" t="s">
+        <v>284</v>
+      </c>
+      <c r="I24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25">
+        <v>1.2800000000000001E-7</v>
+      </c>
+      <c r="H25" t="s">
+        <v>284</v>
+      </c>
+      <c r="I25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26">
+        <v>1.2800000000000001E-7</v>
+      </c>
+      <c r="H26" t="s">
+        <v>284</v>
+      </c>
+      <c r="I26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27">
+        <v>1.2800000000000001E-7</v>
+      </c>
+      <c r="H27" t="s">
+        <v>284</v>
+      </c>
+      <c r="I27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28">
+        <v>1.2800000000000001E-7</v>
+      </c>
+      <c r="H28" t="s">
+        <v>284</v>
+      </c>
+      <c r="I28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29">
+        <v>6.0487630000000008E-2</v>
+      </c>
+      <c r="H29" t="s">
+        <v>284</v>
+      </c>
+      <c r="I29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>284</v>
+      </c>
+      <c r="I30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31">
+        <v>3.9500000000000004E-3</v>
+      </c>
+      <c r="H31" t="s">
+        <v>284</v>
+      </c>
+      <c r="I31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32">
+        <v>1.316535E-3</v>
+      </c>
+      <c r="H32" t="s">
+        <v>284</v>
+      </c>
+      <c r="I32" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33">
+        <v>1.9572249999999999E-3</v>
+      </c>
+      <c r="H33" t="s">
+        <v>284</v>
+      </c>
+      <c r="I33" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>80</v>
+      </c>
+      <c r="G34">
+        <v>2.5043000000000001E-3</v>
+      </c>
+      <c r="H34" t="s">
+        <v>284</v>
+      </c>
+      <c r="I34" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>83</v>
+      </c>
+      <c r="G35">
+        <v>3.1066750000000001E-3</v>
+      </c>
+      <c r="H35" t="s">
+        <v>284</v>
+      </c>
+      <c r="I35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36">
+        <v>6.4492200000000002E-9</v>
+      </c>
+      <c r="H36" t="s">
+        <v>284</v>
+      </c>
+      <c r="I36" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37">
+        <v>1.61595E-8</v>
+      </c>
+      <c r="H37" t="s">
+        <v>284</v>
+      </c>
+      <c r="I37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>93</v>
+      </c>
+      <c r="G38">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H38" t="s">
+        <v>284</v>
+      </c>
+      <c r="I38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>95</v>
+      </c>
+      <c r="G39">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H39" t="s">
+        <v>284</v>
+      </c>
+      <c r="I39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>97</v>
+      </c>
+      <c r="G40">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H40" t="s">
+        <v>284</v>
+      </c>
+      <c r="I40" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>98</v>
+      </c>
+      <c r="G41">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H41" t="s">
+        <v>284</v>
+      </c>
+      <c r="I41" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H42" t="s">
+        <v>284</v>
+      </c>
+      <c r="I42" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>102</v>
+      </c>
+      <c r="G43">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H43" t="s">
+        <v>284</v>
+      </c>
+      <c r="I43" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>105</v>
+      </c>
+      <c r="G44">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H44" t="s">
+        <v>284</v>
+      </c>
+      <c r="I44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>108</v>
+      </c>
+      <c r="G45">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H45" t="s">
+        <v>284</v>
+      </c>
+      <c r="I45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>111</v>
+      </c>
+      <c r="G46">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H46" t="s">
+        <v>284</v>
+      </c>
+      <c r="I46" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>112</v>
+      </c>
+      <c r="G47">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H47" t="s">
+        <v>284</v>
+      </c>
+      <c r="I47" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>114</v>
+      </c>
+      <c r="G48">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H48" t="s">
+        <v>284</v>
+      </c>
+      <c r="I48" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>116</v>
+      </c>
+      <c r="G49">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H49" t="s">
+        <v>284</v>
+      </c>
+      <c r="I49" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>91</v>
+      </c>
+      <c r="B50" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>117</v>
+      </c>
+      <c r="G50">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H50" t="s">
+        <v>284</v>
+      </c>
+      <c r="I50" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G51">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H51" t="s">
+        <v>284</v>
+      </c>
+      <c r="I51" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>121</v>
+      </c>
+      <c r="G52">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H52" t="s">
+        <v>284</v>
+      </c>
+      <c r="I52" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>123</v>
+      </c>
+      <c r="G53">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H53" t="s">
+        <v>284</v>
+      </c>
+      <c r="I53" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>126</v>
+      </c>
+      <c r="G54">
+        <v>1.6199999999999999E-8</v>
+      </c>
+      <c r="H54" t="s">
+        <v>284</v>
+      </c>
+      <c r="I54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>128</v>
+      </c>
+      <c r="G55">
+        <v>2.8528200000000001E-9</v>
+      </c>
+      <c r="H55" t="s">
+        <v>284</v>
+      </c>
+      <c r="I55" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B56" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>130</v>
+      </c>
+      <c r="G56">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H56" t="s">
+        <v>284</v>
+      </c>
+      <c r="I56" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>131</v>
+      </c>
+      <c r="G57">
+        <v>1.6198379999999999E-8</v>
+      </c>
+      <c r="H57" t="s">
+        <v>284</v>
+      </c>
+      <c r="I57" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>134</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58" t="s">
+        <v>284</v>
+      </c>
+      <c r="I58" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>136</v>
+      </c>
+      <c r="B59" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>138</v>
+      </c>
+      <c r="G59">
+        <v>0.86607219999999996</v>
+      </c>
+      <c r="H59" t="s">
+        <v>284</v>
+      </c>
+      <c r="I59" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" t="s">
+        <v>140</v>
+      </c>
+      <c r="C60" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>141</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60" t="s">
+        <v>284</v>
+      </c>
+      <c r="I60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>143</v>
+      </c>
+      <c r="B61" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" t="s">
+        <v>0</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>145</v>
+      </c>
+      <c r="G61">
+        <v>0.85841840000000003</v>
+      </c>
+      <c r="H61" t="s">
+        <v>284</v>
+      </c>
+      <c r="I61" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" t="s">
+        <v>0</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>141</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62" t="s">
+        <v>284</v>
+      </c>
+      <c r="I62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>147</v>
+      </c>
+      <c r="B63" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" t="s">
+        <v>0</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>149</v>
+      </c>
+      <c r="G63">
+        <v>0.50864799999999999</v>
+      </c>
+      <c r="H63" t="s">
+        <v>284</v>
+      </c>
+      <c r="I63" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>150</v>
+      </c>
+      <c r="B64" t="s">
+        <v>92</v>
+      </c>
+      <c r="C64" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>151</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64" t="s">
+        <v>284</v>
+      </c>
+      <c r="I64" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>153</v>
+      </c>
+      <c r="B65" t="s">
+        <v>154</v>
+      </c>
+      <c r="C65" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>155</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>284</v>
+      </c>
+      <c r="I65" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" t="s">
+        <v>0</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>157</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>284</v>
+      </c>
+      <c r="I66" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>160</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>284</v>
+      </c>
+      <c r="I67" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
+        <v>158</v>
+      </c>
+      <c r="B68" t="s">
+        <v>159</v>
+      </c>
+      <c r="C68" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" t="s">
+        <v>161</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>284</v>
+      </c>
+      <c r="I68" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>162</v>
+      </c>
+      <c r="B69" t="s">
+        <v>163</v>
+      </c>
+      <c r="C69" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" t="s">
+        <v>164</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>284</v>
+      </c>
+      <c r="I69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" t="s">
+        <v>162</v>
+      </c>
+      <c r="B70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C70" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" t="s">
+        <v>165</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>284</v>
+      </c>
+      <c r="I70" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" t="s">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>168</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>284</v>
+      </c>
+      <c r="I71" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" t="s">
+        <v>169</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>284</v>
+      </c>
+      <c r="I72" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" t="s">
+        <v>170</v>
+      </c>
+      <c r="B73" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>171</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s">
+        <v>284</v>
+      </c>
+      <c r="I73" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" t="s">
+        <v>167</v>
+      </c>
+      <c r="C74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>172</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>284</v>
+      </c>
+      <c r="I74" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" t="s">
+        <v>173</v>
+      </c>
+      <c r="C75" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>284</v>
+      </c>
+      <c r="I75" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" t="s">
+        <v>173</v>
+      </c>
+      <c r="C76" t="s">
+        <v>27</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76" t="s">
+        <v>284</v>
+      </c>
+      <c r="I76" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" t="s">
+        <v>176</v>
+      </c>
+      <c r="B77" t="s">
+        <v>177</v>
+      </c>
+      <c r="C77" t="s">
+        <v>0</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" t="s">
+        <v>178</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>284</v>
+      </c>
+      <c r="I77" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
+        <v>166</v>
+      </c>
+      <c r="B78" t="s">
+        <v>179</v>
+      </c>
+      <c r="C78" t="s">
+        <v>0</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
+        <v>180</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>284</v>
+      </c>
+      <c r="I78" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" t="s">
+        <v>181</v>
+      </c>
+      <c r="B79" t="s">
+        <v>182</v>
+      </c>
+      <c r="C79" t="s">
+        <v>183</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" t="s">
+        <v>184</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79" t="s">
+        <v>284</v>
+      </c>
+      <c r="I79" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" t="s">
+        <v>182</v>
+      </c>
+      <c r="C80" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" t="s">
+        <v>185</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80" t="s">
+        <v>284</v>
+      </c>
+      <c r="I80" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
+        <v>181</v>
+      </c>
+      <c r="B81" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" t="s">
+        <v>48</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" t="s">
+        <v>186</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81" t="s">
+        <v>284</v>
+      </c>
+      <c r="I81" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" t="s">
+        <v>187</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" t="s">
+        <v>188</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82" t="s">
+        <v>284</v>
+      </c>
+      <c r="I82" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" t="s">
+        <v>166</v>
+      </c>
+      <c r="B83" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" t="s">
+        <v>0</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" t="s">
+        <v>190</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>284</v>
+      </c>
+      <c r="I83" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" t="s">
+        <v>191</v>
+      </c>
+      <c r="B84" t="s">
+        <v>192</v>
+      </c>
+      <c r="C84" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>193</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84" t="s">
+        <v>284</v>
+      </c>
+      <c r="I84" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" t="s">
+        <v>194</v>
+      </c>
+      <c r="B85" t="s">
+        <v>195</v>
+      </c>
+      <c r="C85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>196</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85" t="s">
+        <v>284</v>
+      </c>
+      <c r="I85" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" t="s">
+        <v>197</v>
+      </c>
+      <c r="B86" t="s">
+        <v>198</v>
+      </c>
+      <c r="C86" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86" t="s">
+        <v>284</v>
+      </c>
+      <c r="I86" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" t="s">
+        <v>200</v>
+      </c>
+      <c r="B87" t="s">
+        <v>201</v>
+      </c>
+      <c r="C87" t="s">
+        <v>0</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" t="s">
+        <v>202</v>
+      </c>
+      <c r="G87">
+        <v>0.179983</v>
+      </c>
+      <c r="H87" t="s">
+        <v>284</v>
+      </c>
+      <c r="I87" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" t="s">
+        <v>66</v>
+      </c>
+      <c r="B88" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>68</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88" t="s">
+        <v>284</v>
+      </c>
+      <c r="I88" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" t="s">
+        <v>204</v>
+      </c>
+      <c r="B89" t="s">
+        <v>205</v>
+      </c>
+      <c r="C89" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" t="s">
+        <v>206</v>
+      </c>
+      <c r="G89">
+        <v>1.1141E-2</v>
+      </c>
+      <c r="H89" t="s">
+        <v>284</v>
+      </c>
+      <c r="I89" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" t="s">
+        <v>208</v>
+      </c>
+      <c r="B90" t="s">
+        <v>209</v>
+      </c>
+      <c r="C90" t="s">
+        <v>0</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>210</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90" t="s">
+        <v>284</v>
+      </c>
+      <c r="I90" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" t="s">
+        <v>212</v>
+      </c>
+      <c r="C91" t="s">
+        <v>0</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" t="s">
+        <v>213</v>
+      </c>
+      <c r="G91">
+        <v>4.0999999999999999E-7</v>
+      </c>
+      <c r="H91" t="s">
+        <v>284</v>
+      </c>
+      <c r="I91" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" t="s">
+        <v>215</v>
+      </c>
+      <c r="B92" t="s">
+        <v>216</v>
+      </c>
+      <c r="C92" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" t="s">
+        <v>217</v>
+      </c>
+      <c r="G92">
+        <v>1.148E-7</v>
+      </c>
+      <c r="H92" t="s">
+        <v>284</v>
+      </c>
+      <c r="I92" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
+        <v>218</v>
+      </c>
+      <c r="B93" t="s">
+        <v>99</v>
+      </c>
+      <c r="C93" t="s">
+        <v>0</v>
+      </c>
+      <c r="D93" t="s">
+        <v>1</v>
+      </c>
+      <c r="F93" t="s">
+        <v>219</v>
+      </c>
+      <c r="G93">
+        <v>6.5600000000000005E-7</v>
+      </c>
+      <c r="H93" t="s">
+        <v>284</v>
+      </c>
+      <c r="I93" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" t="s">
+        <v>220</v>
+      </c>
+      <c r="B94" t="s">
+        <v>99</v>
+      </c>
+      <c r="C94" t="s">
+        <v>0</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>221</v>
+      </c>
+      <c r="G94">
+        <v>1.6350799999999999E-6</v>
+      </c>
+      <c r="H94" t="s">
+        <v>284</v>
+      </c>
+      <c r="I94" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
+        <v>220</v>
+      </c>
+      <c r="B95" t="s">
+        <v>115</v>
+      </c>
+      <c r="C95" t="s">
+        <v>27</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>222</v>
+      </c>
+      <c r="G95">
+        <v>1.6350799999999999E-6</v>
+      </c>
+      <c r="H95" t="s">
+        <v>284</v>
+      </c>
+      <c r="I95" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
+        <v>220</v>
+      </c>
+      <c r="B96" t="s">
+        <v>109</v>
+      </c>
+      <c r="C96" t="s">
+        <v>110</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
+        <v>223</v>
+      </c>
+      <c r="G96">
+        <v>1.6350799999999999E-6</v>
+      </c>
+      <c r="H96" t="s">
+        <v>284</v>
+      </c>
+      <c r="I96" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" t="s">
+        <v>220</v>
+      </c>
+      <c r="B97" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" t="s">
+        <v>104</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
+        <v>224</v>
+      </c>
+      <c r="G97">
+        <v>1.6350799999999999E-6</v>
+      </c>
+      <c r="H97" t="s">
+        <v>284</v>
+      </c>
+      <c r="I97" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98" t="s">
+        <v>225</v>
+      </c>
+      <c r="C98" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98">
+        <v>1.6350799999999999E-6</v>
+      </c>
+      <c r="H98" t="s">
+        <v>284</v>
+      </c>
+      <c r="I98" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" t="s">
+        <v>106</v>
+      </c>
+      <c r="C99" t="s">
+        <v>107</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" t="s">
+        <v>227</v>
+      </c>
+      <c r="G99">
+        <v>1.6350799999999999E-6</v>
+      </c>
+      <c r="H99" t="s">
+        <v>284</v>
+      </c>
+      <c r="I99" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" t="s">
+        <v>220</v>
+      </c>
+      <c r="B100" t="s">
+        <v>228</v>
+      </c>
+      <c r="C100" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" t="s">
+        <v>229</v>
+      </c>
+      <c r="G100">
+        <v>1.6350799999999999E-6</v>
+      </c>
+      <c r="H100" t="s">
+        <v>284</v>
+      </c>
+      <c r="I100" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" t="s">
+        <v>230</v>
+      </c>
+      <c r="C101" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" t="s">
+        <v>231</v>
+      </c>
+      <c r="G101">
+        <v>1.6350799999999999E-6</v>
+      </c>
+      <c r="H101" t="s">
+        <v>284</v>
+      </c>
+      <c r="I101" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" t="s">
+        <v>232</v>
+      </c>
+      <c r="B102" t="s">
+        <v>233</v>
+      </c>
+      <c r="C102" t="s">
+        <v>0</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" t="s">
+        <v>234</v>
+      </c>
+      <c r="G102">
+        <v>1.64E-6</v>
+      </c>
+      <c r="H102" t="s">
+        <v>284</v>
+      </c>
+      <c r="I102" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" t="s">
+        <v>235</v>
+      </c>
+      <c r="B103" t="s">
+        <v>236</v>
+      </c>
+      <c r="C103" t="s">
+        <v>0</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" t="s">
+        <v>237</v>
+      </c>
+      <c r="G103">
+        <v>4.53E-2</v>
+      </c>
+      <c r="H103" t="s">
+        <v>284</v>
+      </c>
+      <c r="I103" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" t="s">
+        <v>238</v>
+      </c>
+      <c r="B104" t="s">
+        <v>239</v>
+      </c>
+      <c r="C104" t="s">
+        <v>0</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1</v>
+      </c>
+      <c r="F104" t="s">
+        <v>240</v>
+      </c>
+      <c r="G104">
+        <v>0.177644</v>
+      </c>
+      <c r="H104" t="s">
+        <v>284</v>
+      </c>
+      <c r="I104" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" t="s">
+        <v>0</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1</v>
+      </c>
+      <c r="F105" t="s">
+        <v>210</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105" t="s">
+        <v>284</v>
+      </c>
+      <c r="I105" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" t="s">
+        <v>242</v>
+      </c>
+      <c r="B106" t="s">
+        <v>243</v>
+      </c>
+      <c r="C106" t="s">
+        <v>0</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" t="s">
+        <v>244</v>
+      </c>
+      <c r="G106">
+        <v>0.1649185</v>
+      </c>
+      <c r="H106" t="s">
+        <v>284</v>
+      </c>
+      <c r="I106" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" t="s">
+        <v>245</v>
+      </c>
+      <c r="B107" t="s">
+        <v>246</v>
+      </c>
+      <c r="C107" t="s">
+        <v>0</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1</v>
+      </c>
+      <c r="F107" t="s">
+        <v>247</v>
+      </c>
+      <c r="G107">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="H107" t="s">
+        <v>284</v>
+      </c>
+      <c r="I107" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" t="s">
+        <v>248</v>
+      </c>
+      <c r="B108" t="s">
+        <v>249</v>
+      </c>
+      <c r="C108" t="s">
+        <v>0</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1</v>
+      </c>
+      <c r="F108" t="s">
+        <v>250</v>
+      </c>
+      <c r="G108">
+        <v>7.2764999999999997E-6</v>
+      </c>
+      <c r="H108" t="s">
+        <v>284</v>
+      </c>
+      <c r="I108" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" t="s">
+        <v>252</v>
+      </c>
+      <c r="B109" t="s">
+        <v>253</v>
+      </c>
+      <c r="C109" t="s">
+        <v>0</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1</v>
+      </c>
+      <c r="F109" t="s">
+        <v>254</v>
+      </c>
+      <c r="G109">
+        <v>5.1479399999999997E-6</v>
+      </c>
+      <c r="H109" t="s">
+        <v>284</v>
+      </c>
+      <c r="I109" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" t="s">
+        <v>255</v>
+      </c>
+      <c r="B110" t="s">
+        <v>256</v>
+      </c>
+      <c r="C110" t="s">
+        <v>187</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1</v>
+      </c>
+      <c r="F110" t="s">
+        <v>257</v>
+      </c>
+      <c r="G110">
+        <v>1.214955E-6</v>
+      </c>
+      <c r="H110" t="s">
+        <v>284</v>
+      </c>
+      <c r="I110" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" t="s">
+        <v>255</v>
+      </c>
+      <c r="B111" t="s">
+        <v>256</v>
+      </c>
+      <c r="C111" t="s">
+        <v>258</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1</v>
+      </c>
+      <c r="F111" t="s">
+        <v>259</v>
+      </c>
+      <c r="G111">
+        <v>1.214955E-6</v>
+      </c>
+      <c r="H111" t="s">
+        <v>284</v>
+      </c>
+      <c r="I111" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" t="s">
+        <v>255</v>
+      </c>
+      <c r="B112" t="s">
+        <v>256</v>
+      </c>
+      <c r="C112" t="s">
+        <v>27</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1</v>
+      </c>
+      <c r="F112" t="s">
+        <v>260</v>
+      </c>
+      <c r="G112">
+        <v>1.214955E-6</v>
+      </c>
+      <c r="H112" t="s">
+        <v>284</v>
+      </c>
+      <c r="I112" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" t="s">
+        <v>261</v>
+      </c>
+      <c r="B113" t="s">
+        <v>262</v>
+      </c>
+      <c r="C113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1</v>
+      </c>
+      <c r="F113" t="s">
+        <v>263</v>
+      </c>
+      <c r="G113">
+        <v>2.4607800000000001E-6</v>
+      </c>
+      <c r="H113" t="s">
+        <v>284</v>
+      </c>
+      <c r="I113" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" t="s">
+        <v>261</v>
+      </c>
+      <c r="B114" t="s">
+        <v>262</v>
+      </c>
+      <c r="C114" t="s">
+        <v>25</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1</v>
+      </c>
+      <c r="F114" t="s">
+        <v>264</v>
+      </c>
+      <c r="G114">
+        <v>2.4607800000000001E-6</v>
+      </c>
+      <c r="H114" t="s">
+        <v>284</v>
+      </c>
+      <c r="I114" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" t="s">
+        <v>265</v>
+      </c>
+      <c r="B115" t="s">
+        <v>266</v>
+      </c>
+      <c r="C115" t="s">
+        <v>48</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1</v>
+      </c>
+      <c r="F115" t="s">
+        <v>267</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115" t="s">
+        <v>284</v>
+      </c>
+      <c r="I115" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" t="s">
+        <v>268</v>
+      </c>
+      <c r="B116" t="s">
+        <v>269</v>
+      </c>
+      <c r="C116" t="s">
+        <v>0</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1</v>
+      </c>
+      <c r="F116" t="s">
+        <v>270</v>
+      </c>
+      <c r="G116">
+        <v>2.1484700000000001E-5</v>
+      </c>
+      <c r="H116" t="s">
+        <v>284</v>
+      </c>
+      <c r="I116" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" t="s">
+        <v>272</v>
+      </c>
+      <c r="B117" t="s">
+        <v>273</v>
+      </c>
+      <c r="C117" t="s">
+        <v>0</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1</v>
+      </c>
+      <c r="F117" t="s">
+        <v>274</v>
+      </c>
+      <c r="G117">
+        <v>0.73967399999999994</v>
+      </c>
+      <c r="H117" t="s">
+        <v>284</v>
+      </c>
+      <c r="I117" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" t="s">
+        <v>132</v>
+      </c>
+      <c r="B118" t="s">
+        <v>133</v>
+      </c>
+      <c r="C118" t="s">
+        <v>0</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1</v>
+      </c>
+      <c r="F118" t="s">
+        <v>134</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118" t="s">
+        <v>284</v>
+      </c>
+      <c r="I118" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" t="s">
+        <v>276</v>
+      </c>
+      <c r="B119" t="s">
+        <v>277</v>
+      </c>
+      <c r="C119" t="s">
+        <v>0</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1</v>
+      </c>
+      <c r="F119" t="s">
+        <v>278</v>
+      </c>
+      <c r="G119">
+        <v>4.4549999999999998E-3</v>
+      </c>
+      <c r="H119" t="s">
+        <v>284</v>
+      </c>
+      <c r="I119" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" t="s">
+        <v>280</v>
+      </c>
+      <c r="B120" t="s">
+        <v>281</v>
+      </c>
+      <c r="C120" t="s">
+        <v>0</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1</v>
+      </c>
+      <c r="F120" t="s">
+        <v>282</v>
+      </c>
+      <c r="G120">
+        <v>0.48872700000000002</v>
+      </c>
+      <c r="H120" t="s">
+        <v>284</v>
+      </c>
+      <c r="I120" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
